--- a/excel/universities/tampere-university.xlsx
+++ b/excel/universities/tampere-university.xlsx
@@ -115,7 +115,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university</t>
+          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university/applying-to-university-masters-programmes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -125,27 +125,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t xml:space="preserve">University master's programmes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autumn</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Possible scholarship and early-bird schemes</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fill program-specific information here</t>
+          <t xml:space="preserve">University-level master's admissions timeline for autumn 2026 is published centrally on TUNI.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -229,7 +229,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">University master's programmes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -239,27 +239,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-12-15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university</t>
+          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university/applying-to-university-masters-programmes</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify annual deadlines</t>
+          <t xml:space="preserve">Attachment deadline 2026-01-12; results on 2026-03-13; early-bird acceptance deadline 2026-03-27.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -275,7 +275,7 @@
 
 <file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -333,30 +333,156 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">University master's programmes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport</t>
+          <t xml:space="preserve">Degree certificate</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Completed-degree applicants must later submit officially certified documents by 2026-05-29.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university/applying-to-university-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University master's programmes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latest transcript is accepted for unfinished degrees during the application phase.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university/applying-to-university-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University master's programmes</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of language proficiency</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere requires proof of proficiency in the language of instruction.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university/applying-to-university-masters-programmes/faq-on-applying</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University master's programmes</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific documents</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check programme</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme pages may require motivation letter CV portfolio or interview.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university/applying-to-university-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -369,7 +495,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -420,15 +546,30 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">citation_source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_last_checked</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t xml:space="preserve">official_profile_url</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">email</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">last_verified</t>
         </is>
@@ -442,55 +583,70 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department Name</t>
+          <t xml:space="preserve">Research Centre of Gameful Realities</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor Name</t>
+          <t xml:space="preserve">Juho Hamari</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve">Professor of Gamification</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Area 1; Research Area 2</t>
+          <t xml:space="preserve">Gamification; Game-based learning; Motivational systems; Extended reality; HCI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t xml:space="preserve">https://www.researchgate.net/profile/Juho-Hamari</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://scholar.google.com/citations?user=tKMlAegAAAAJ</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50000+</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.tuni.fi/en</t>
+          <t xml:space="preserve">Tampere University research centre page; ResearchGate profile</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://research.tuni.fi/gameful-realities/gamification-group/</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juho.hamari@tuni.fi</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere research centre page states 50000+ citations and links both Google Scholar and ResearchGate.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>

--- a/excel/universities/tampere-university.xlsx
+++ b/excel/universities/tampere-university.xlsx
@@ -20,7 +20,8 @@
     <sheet name="UniversityInfo" sheetId="1" r:id="rId1"/>
     <sheet name="Deadlines" sheetId="2" r:id="rId2"/>
     <sheet name="Documents" sheetId="3" r:id="rId3"/>
-    <sheet name="Professors" sheetId="4" r:id="rId4"/>
+    <sheet name="Departments" sheetId="4" r:id="rId4"/>
+    <sheet name="Professors" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -495,6 +496,721 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">university_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unit_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unit_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">parent_unit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">campus_or_city</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">focus_areas</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">official_url</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">last_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Built Environment</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Architecture; Civil engineering; Built environment</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Education and Culture</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education; Humanities; Languages</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology and Communication Sciences</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computing; Media; Information studies</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Engineering and Natural Sciences</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering; Natural sciences</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Management and Business</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Management; Economics; Administrative sciences</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Medicine and Health Technology</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medicine; Health technology</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social sciences; Psychology; Health sciences</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">History, Philosophy and Literary Studies</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">History; Philosophy; Literature</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties-and-units/faculty-social-sciences</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty unit list.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social Research</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social research</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties-and-units/faculty-social-sciences</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty unit list.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Welfare Sciences</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social work; Welfare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties-and-units/faculty-social-sciences</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty unit list.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health Sciences</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health sciences</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties-and-units/faculty-social-sciences</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty unit list.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automation Technology and Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Engineering and Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automation; Mechanical engineering</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties-and-units/faculty-engineering-and-natural-sciences</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty unit list.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Materials Science and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Engineering and Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Materials science; Environmental engineering</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties-and-units/faculty-engineering-and-natural-sciences</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty unit list.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physics</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Engineering and Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physics</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties-and-units/faculty-engineering-and-natural-sciences</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty unit list.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
